--- a/outputs/evaluation/architecture/validation/CF_M04/run_2/CF_M04_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_2/CF_M04_arch_eval_by_type.xlsx
@@ -614,19 +614,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.625</v>
+        <v>0.5556</v>
       </c>
       <c r="H7" t="n">
         <v>0.8333</v>
@@ -698,22 +698,22 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
